--- a/backend/exports/master_export.xlsx
+++ b/backend/exports/master_export.xlsx
@@ -1303,7 +1303,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS142"/>
+  <dimension ref="A1:AS145"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17311,16 +17311,328 @@
         <v>2026-06-13T17:31:21.979Z</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>6a2d951786f4fda65896eff6</v>
+      </c>
+      <c r="B143" t="str">
+        <v>TCM-2026-0143</v>
+      </c>
+      <c r="D143" t="str">
+        <v>false</v>
+      </c>
+      <c r="E143" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="F143" t="str">
+        <v>2026-06-13T18:30:00.000Z</v>
+      </c>
+      <c r="G143" t="str">
+        <v>4:00 PM – 6:00 PM</v>
+      </c>
+      <c r="H143" t="str">
+        <v>false</v>
+      </c>
+      <c r="I143" t="str">
+        <v>0</v>
+      </c>
+      <c r="J143" t="str">
+        <v>false</v>
+      </c>
+      <c r="K143" t="str">
+        <v>[{"customDetails":null,"productId":"6a299407c4fc5fbd6d56d026","name":"Nutty Truffle","qty":1,"price":599,"originalPrice":780,"couponCode":null,"discountAmount":181,"image":"https://res.cloudinary.com/djkfvoxpx/image/upload/v1781175836/chocolate-cakes/qrhw6a2hkmotuih7rf7z.jpg","isCustomCake":false,"_id":"6a2d951786f4fda65896eff7","sku":"NUT-CAK-ST-KG-260613-001"}]</v>
+      </c>
+      <c r="L143" t="str">
+        <v>599</v>
+      </c>
+      <c r="M143" t="str">
+        <v>0</v>
+      </c>
+      <c r="N143" t="str">
+        <v>30</v>
+      </c>
+      <c r="O143" t="str">
+        <v>12</v>
+      </c>
+      <c r="P143" t="str">
+        <v>108</v>
+      </c>
+      <c r="Q143" t="str">
+        <v>749</v>
+      </c>
+      <c r="R143" t="str">
+        <v>ONLINE</v>
+      </c>
+      <c r="S143" t="str">
+        <v>failed</v>
+      </c>
+      <c r="T143" t="str">
+        <v>confirmed</v>
+      </c>
+      <c r="U143" t="str">
+        <v>pending</v>
+      </c>
+      <c r="V143" t="str">
+        <v>Kavin M M</v>
+      </c>
+      <c r="W143" t="str">
+        <v>9600732162</v>
+      </c>
+      <c r="X143" t="str">
+        <v>hm</v>
+      </c>
+      <c r="Y143" t="str">
+        <v>jh</v>
+      </c>
+      <c r="Z143" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="AA143" t="str">
+        <v>641001</v>
+      </c>
+      <c r="AB143" t="str">
+        <v>11.012688777241518</v>
+      </c>
+      <c r="AC143" t="str">
+        <v>76.91418185946593</v>
+      </c>
+      <c r="AD143" t="str">
+        <v>order_T1CTW6gIvIvTnw</v>
+      </c>
+      <c r="AE143" t="str">
+        <v>2026-06-13T17:36:23.115Z</v>
+      </c>
+      <c r="AF143" t="str">
+        <v>2026-06-13T17:36:23.196Z</v>
+      </c>
+      <c r="AG143" t="str">
+        <v>2026-06-13T17:36:33.931Z</v>
+      </c>
+      <c r="AJ143" t="str">
+        <v>TCM-2026-0143</v>
+      </c>
+      <c r="AO143" t="str">
+        <v>2026-06-13T17:36:34.307Z</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>6a2d952486f4fda65896effb</v>
+      </c>
+      <c r="B144" t="str">
+        <v>TCM-2026-0144</v>
+      </c>
+      <c r="D144" t="str">
+        <v>false</v>
+      </c>
+      <c r="E144" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="F144" t="str">
+        <v>2026-06-13T18:30:00.000Z</v>
+      </c>
+      <c r="G144" t="str">
+        <v>4:00 PM – 6:00 PM</v>
+      </c>
+      <c r="H144" t="str">
+        <v>false</v>
+      </c>
+      <c r="I144" t="str">
+        <v>0</v>
+      </c>
+      <c r="J144" t="str">
+        <v>false</v>
+      </c>
+      <c r="K144" t="str">
+        <v>[{"customDetails":null,"productId":"6a299407c4fc5fbd6d56d026","name":"Nutty Truffle","qty":1,"price":599,"originalPrice":780,"couponCode":null,"discountAmount":181,"image":"https://res.cloudinary.com/djkfvoxpx/image/upload/v1781175836/chocolate-cakes/qrhw6a2hkmotuih7rf7z.jpg","isCustomCake":false,"_id":"6a2d952486f4fda65896effc","sku":"NUT-CAK-ST-KG-260613-001"}]</v>
+      </c>
+      <c r="L144" t="str">
+        <v>599</v>
+      </c>
+      <c r="M144" t="str">
+        <v>0</v>
+      </c>
+      <c r="N144" t="str">
+        <v>30</v>
+      </c>
+      <c r="O144" t="str">
+        <v>12</v>
+      </c>
+      <c r="P144" t="str">
+        <v>108</v>
+      </c>
+      <c r="Q144" t="str">
+        <v>749</v>
+      </c>
+      <c r="R144" t="str">
+        <v>ONLINE</v>
+      </c>
+      <c r="S144" t="str">
+        <v>failed</v>
+      </c>
+      <c r="T144" t="str">
+        <v>confirmed</v>
+      </c>
+      <c r="U144" t="str">
+        <v>pending</v>
+      </c>
+      <c r="V144" t="str">
+        <v>Kavin M M</v>
+      </c>
+      <c r="W144" t="str">
+        <v>9600732162</v>
+      </c>
+      <c r="X144" t="str">
+        <v>hm</v>
+      </c>
+      <c r="Y144" t="str">
+        <v>jh</v>
+      </c>
+      <c r="Z144" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="AA144" t="str">
+        <v>641001</v>
+      </c>
+      <c r="AB144" t="str">
+        <v>11.012688777241518</v>
+      </c>
+      <c r="AC144" t="str">
+        <v>76.91418185946593</v>
+      </c>
+      <c r="AD144" t="str">
+        <v>order_T1CTkadPNSw1tN</v>
+      </c>
+      <c r="AE144" t="str">
+        <v>2026-06-13T17:36:36.416Z</v>
+      </c>
+      <c r="AF144" t="str">
+        <v>2026-06-13T17:36:36.424Z</v>
+      </c>
+      <c r="AG144" t="str">
+        <v>2026-06-13T17:37:58.130Z</v>
+      </c>
+      <c r="AJ144" t="str">
+        <v>TCM-2026-0144</v>
+      </c>
+      <c r="AO144" t="str">
+        <v>2026-06-13T17:37:58.713Z</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>6a2d957886f4fda65896f002</v>
+      </c>
+      <c r="B145" t="str">
+        <v>TCM-2026-0145</v>
+      </c>
+      <c r="D145" t="str">
+        <v>false</v>
+      </c>
+      <c r="E145" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="F145" t="str">
+        <v>2026-06-13T18:30:00.000Z</v>
+      </c>
+      <c r="G145" t="str">
+        <v>4:00 PM – 6:00 PM</v>
+      </c>
+      <c r="H145" t="str">
+        <v>false</v>
+      </c>
+      <c r="I145" t="str">
+        <v>0</v>
+      </c>
+      <c r="J145" t="str">
+        <v>false</v>
+      </c>
+      <c r="K145" t="str">
+        <v>[{"customDetails":null,"productId":"6a299407c4fc5fbd6d56d026","name":"Nutty Truffle","qty":1,"price":599,"originalPrice":780,"couponCode":null,"discountAmount":181,"image":"https://res.cloudinary.com/djkfvoxpx/image/upload/v1781175836/chocolate-cakes/qrhw6a2hkmotuih7rf7z.jpg","isCustomCake":false,"_id":"6a2d957886f4fda65896f003","sku":"NUT-CAK-ST-KG-260613-001"}]</v>
+      </c>
+      <c r="L145" t="str">
+        <v>599</v>
+      </c>
+      <c r="M145" t="str">
+        <v>0</v>
+      </c>
+      <c r="N145" t="str">
+        <v>30</v>
+      </c>
+      <c r="O145" t="str">
+        <v>12</v>
+      </c>
+      <c r="P145" t="str">
+        <v>108</v>
+      </c>
+      <c r="Q145" t="str">
+        <v>749</v>
+      </c>
+      <c r="R145" t="str">
+        <v>ONLINE</v>
+      </c>
+      <c r="S145" t="str">
+        <v>failed</v>
+      </c>
+      <c r="T145" t="str">
+        <v>confirmed</v>
+      </c>
+      <c r="U145" t="str">
+        <v>pending</v>
+      </c>
+      <c r="V145" t="str">
+        <v>Kavin M M</v>
+      </c>
+      <c r="W145" t="str">
+        <v>9600732162</v>
+      </c>
+      <c r="X145" t="str">
+        <v>hm</v>
+      </c>
+      <c r="Y145" t="str">
+        <v>jh</v>
+      </c>
+      <c r="Z145" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="AA145" t="str">
+        <v>641001</v>
+      </c>
+      <c r="AB145" t="str">
+        <v>11.012688777241518</v>
+      </c>
+      <c r="AC145" t="str">
+        <v>76.91418185946593</v>
+      </c>
+      <c r="AD145" t="str">
+        <v>order_T1CVEWutXOHYSU</v>
+      </c>
+      <c r="AE145" t="str">
+        <v>2026-06-13T17:38:00.644Z</v>
+      </c>
+      <c r="AF145" t="str">
+        <v>2026-06-13T17:38:00.651Z</v>
+      </c>
+      <c r="AG145" t="str">
+        <v>2026-06-13T17:38:07.326Z</v>
+      </c>
+      <c r="AJ145" t="str">
+        <v>TCM-2026-0145</v>
+      </c>
+      <c r="AO145" t="str">
+        <v>2026-06-13T17:38:07.752Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AS142"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AS145"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M166"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24005,9 +24317,132 @@
         <v>2026-06-13T17:31:53.253Z</v>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>6a2d951986f4fda65896eff9</v>
+      </c>
+      <c r="B164" t="str">
+        <v>6a2d951786f4fda65896eff6</v>
+      </c>
+      <c r="C164" t="str">
+        <v>order_T1CTW6gIvIvTnw</v>
+      </c>
+      <c r="D164" t="str">
+        <v/>
+      </c>
+      <c r="E164" t="str">
+        <v/>
+      </c>
+      <c r="F164" t="str">
+        <v>749</v>
+      </c>
+      <c r="G164" t="str">
+        <v>INR</v>
+      </c>
+      <c r="H164" t="str">
+        <v>created</v>
+      </c>
+      <c r="I164" t="str">
+        <v>razorpay</v>
+      </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
+        <v>2026-06-13T17:36:25.109Z</v>
+      </c>
+      <c r="L164" t="str">
+        <v>2026-06-13T17:36:25.109Z</v>
+      </c>
+      <c r="M164" t="str">
+        <v>2026-06-13T17:36:34.861Z</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>6a2d952586f4fda65896effe</v>
+      </c>
+      <c r="B165" t="str">
+        <v>6a2d952486f4fda65896effb</v>
+      </c>
+      <c r="C165" t="str">
+        <v>order_T1CTkadPNSw1tN</v>
+      </c>
+      <c r="D165" t="str">
+        <v/>
+      </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v>749</v>
+      </c>
+      <c r="G165" t="str">
+        <v>INR</v>
+      </c>
+      <c r="H165" t="str">
+        <v>created</v>
+      </c>
+      <c r="I165" t="str">
+        <v>razorpay</v>
+      </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
+      <c r="K165" t="str">
+        <v>2026-06-13T17:36:37.281Z</v>
+      </c>
+      <c r="L165" t="str">
+        <v>2026-06-13T17:36:37.281Z</v>
+      </c>
+      <c r="M165" t="str">
+        <v>2026-06-13T17:37:59.253Z</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>6a2d957986f4fda65896f006</v>
+      </c>
+      <c r="B166" t="str">
+        <v>6a2d957886f4fda65896f002</v>
+      </c>
+      <c r="C166" t="str">
+        <v>order_T1CVEWutXOHYSU</v>
+      </c>
+      <c r="D166" t="str">
+        <v/>
+      </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" t="str">
+        <v>749</v>
+      </c>
+      <c r="G166" t="str">
+        <v>INR</v>
+      </c>
+      <c r="H166" t="str">
+        <v>created</v>
+      </c>
+      <c r="I166" t="str">
+        <v>razorpay</v>
+      </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
+      <c r="K166" t="str">
+        <v>2026-06-13T17:38:01.998Z</v>
+      </c>
+      <c r="L166" t="str">
+        <v>2026-06-13T17:38:01.998Z</v>
+      </c>
+      <c r="M166" t="str">
+        <v>2026-06-13T17:38:08.422Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M163"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M166"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -31580,7 +32015,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD433"/>
+  <dimension ref="A1:AD439"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -59862,9 +60297,459 @@
         <v>1098</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>6a2d952586f4fda65896efff</v>
+      </c>
+      <c r="B434" t="str">
+        <v>6a2d951786f4fda65896eff6</v>
+      </c>
+      <c r="C434" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="D434" t="str">
+        <v>user</v>
+      </c>
+      <c r="E434" t="str">
+        <v>payment_failed</v>
+      </c>
+      <c r="F434" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="G434" t="str">
+        <v>Your payment of ₹749 for order #TCM-2026-0143 failed. Please retry.</v>
+      </c>
+      <c r="H434" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="I434" t="str">
+        <v>true</v>
+      </c>
+      <c r="J434" t="str">
+        <v>false</v>
+      </c>
+      <c r="K434" t="str">
+        <v>false</v>
+      </c>
+      <c r="L434" t="str">
+        <v>false</v>
+      </c>
+      <c r="M434" t="str">
+        <v>2026-06-13T17:36:37.285Z</v>
+      </c>
+      <c r="N434" t="str">
+        <v>2026-06-13T17:36:37.287Z</v>
+      </c>
+      <c r="O434" t="str">
+        <v>2026-06-13T17:36:37.287Z</v>
+      </c>
+      <c r="P434" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q434" t="str">
+        <v>2026-06-13T17:36:38.121Z</v>
+      </c>
+      <c r="R434" t="str">
+        <v>Payment Failed 🔴</v>
+      </c>
+      <c r="S434" t="str">
+        <v>payment_failed</v>
+      </c>
+      <c r="T434" t="str">
+        <v>6a2d951786f4fda65896eff6</v>
+      </c>
+      <c r="U434" t="str">
+        <v>/account/orders/6a2d951786f4fda65896eff6</v>
+      </c>
+    </row>
+    <row r="435" xml:space="preserve">
+      <c r="A435" t="str">
+        <v>6a2d952886f4fda65896f000</v>
+      </c>
+      <c r="B435" t="str">
+        <v>6a2d951786f4fda65896eff6</v>
+      </c>
+      <c r="C435" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="D435" t="str">
+        <v>admin</v>
+      </c>
+      <c r="E435" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="F435" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="G435" t="str" xml:space="preserve">
+        <v xml:space="preserve">Order #TCM-2026-0143 payment failed.
+Reason: User closed payment window
+Customer: Kavin M M
+Phone: 9600732162
+Email: mmkavin96@gmail.com
+Amount: ₹749</v>
+      </c>
+      <c r="H435" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="I435" t="str">
+        <v>true</v>
+      </c>
+      <c r="J435" t="str">
+        <v>false</v>
+      </c>
+      <c r="K435" t="str">
+        <v>false</v>
+      </c>
+      <c r="L435" t="str">
+        <v>false</v>
+      </c>
+      <c r="M435" t="str">
+        <v>2026-06-13T17:36:40.546Z</v>
+      </c>
+      <c r="N435" t="str">
+        <v>2026-06-13T17:36:40.547Z</v>
+      </c>
+      <c r="O435" t="str">
+        <v>2026-06-13T17:36:40.547Z</v>
+      </c>
+      <c r="P435" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q435" t="str">
+        <v>2026-06-13T17:36:40.951Z</v>
+      </c>
+      <c r="R435" t="str">
+        <v>⚠️ Payment Failed</v>
+      </c>
+      <c r="S435" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="T435" t="str">
+        <v>6a2d951786f4fda65896eff6</v>
+      </c>
+      <c r="U435" t="str">
+        <v>/admin/orders</v>
+      </c>
+      <c r="V435" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="W435" t="str">
+        <v>9600732162</v>
+      </c>
+      <c r="X435" t="str">
+        <v>749</v>
+      </c>
+      <c r="AB435" t="str">
+        <v>mmkavin96@gmail.com</v>
+      </c>
+      <c r="AC435" t="str">
+        <v>User closed payment window</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>6a2d957886f4fda65896f005</v>
+      </c>
+      <c r="B436" t="str">
+        <v>6a2d952486f4fda65896effb</v>
+      </c>
+      <c r="C436" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="D436" t="str">
+        <v>user</v>
+      </c>
+      <c r="E436" t="str">
+        <v>payment_failed</v>
+      </c>
+      <c r="F436" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="G436" t="str">
+        <v>Your payment of ₹749 for order #TCM-2026-0144 failed. Please retry.</v>
+      </c>
+      <c r="H436" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="I436" t="str">
+        <v>true</v>
+      </c>
+      <c r="J436" t="str">
+        <v>false</v>
+      </c>
+      <c r="K436" t="str">
+        <v>false</v>
+      </c>
+      <c r="L436" t="str">
+        <v>false</v>
+      </c>
+      <c r="M436" t="str">
+        <v>2026-06-13T17:38:00.828Z</v>
+      </c>
+      <c r="N436" t="str">
+        <v>2026-06-13T17:38:00.851Z</v>
+      </c>
+      <c r="O436" t="str">
+        <v>2026-06-13T17:38:00.851Z</v>
+      </c>
+      <c r="P436" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q436" t="str">
+        <v>2026-06-13T17:38:01.361Z</v>
+      </c>
+      <c r="R436" t="str">
+        <v>Payment Failed 🔴</v>
+      </c>
+      <c r="S436" t="str">
+        <v>payment_failed</v>
+      </c>
+      <c r="T436" t="str">
+        <v>6a2d952486f4fda65896effb</v>
+      </c>
+      <c r="U436" t="str">
+        <v>/account/orders/6a2d952486f4fda65896effb</v>
+      </c>
+    </row>
+    <row r="437" xml:space="preserve">
+      <c r="A437" t="str">
+        <v>6a2d957c86f4fda65896f007</v>
+      </c>
+      <c r="B437" t="str">
+        <v>6a2d952486f4fda65896effb</v>
+      </c>
+      <c r="C437" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="D437" t="str">
+        <v>admin</v>
+      </c>
+      <c r="E437" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="F437" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="G437" t="str" xml:space="preserve">
+        <v xml:space="preserve">Order #TCM-2026-0144 payment failed.
+Reason: User closed payment window
+Customer: Kavin M M
+Phone: 9600732162
+Email: mmkavin96@gmail.com
+Amount: ₹749</v>
+      </c>
+      <c r="H437" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="I437" t="str">
+        <v>true</v>
+      </c>
+      <c r="J437" t="str">
+        <v>false</v>
+      </c>
+      <c r="K437" t="str">
+        <v>false</v>
+      </c>
+      <c r="L437" t="str">
+        <v>false</v>
+      </c>
+      <c r="M437" t="str">
+        <v>2026-06-13T17:38:04.717Z</v>
+      </c>
+      <c r="N437" t="str">
+        <v>2026-06-13T17:38:04.718Z</v>
+      </c>
+      <c r="O437" t="str">
+        <v>2026-06-13T17:38:04.718Z</v>
+      </c>
+      <c r="P437" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q437" t="str">
+        <v>2026-06-13T17:38:05.076Z</v>
+      </c>
+      <c r="R437" t="str">
+        <v>⚠️ Payment Failed</v>
+      </c>
+      <c r="S437" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="T437" t="str">
+        <v>6a2d952486f4fda65896effb</v>
+      </c>
+      <c r="U437" t="str">
+        <v>/admin/orders</v>
+      </c>
+      <c r="V437" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="W437" t="str">
+        <v>9600732162</v>
+      </c>
+      <c r="X437" t="str">
+        <v>749</v>
+      </c>
+      <c r="AB437" t="str">
+        <v>mmkavin96@gmail.com</v>
+      </c>
+      <c r="AC437" t="str">
+        <v>User closed payment window</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>6a2d958186f4fda65896f009</v>
+      </c>
+      <c r="B438" t="str">
+        <v>6a2d957886f4fda65896f002</v>
+      </c>
+      <c r="C438" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="D438" t="str">
+        <v>user</v>
+      </c>
+      <c r="E438" t="str">
+        <v>payment_failed</v>
+      </c>
+      <c r="F438" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="G438" t="str">
+        <v>Your payment of ₹749 for order #TCM-2026-0145 failed. Please retry.</v>
+      </c>
+      <c r="H438" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="I438" t="str">
+        <v>true</v>
+      </c>
+      <c r="J438" t="str">
+        <v>false</v>
+      </c>
+      <c r="K438" t="str">
+        <v>false</v>
+      </c>
+      <c r="L438" t="str">
+        <v>false</v>
+      </c>
+      <c r="M438" t="str">
+        <v>2026-06-13T17:38:09.702Z</v>
+      </c>
+      <c r="N438" t="str">
+        <v>2026-06-13T17:38:09.704Z</v>
+      </c>
+      <c r="O438" t="str">
+        <v>2026-06-13T17:38:09.704Z</v>
+      </c>
+      <c r="P438" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q438" t="str">
+        <v>2026-06-13T17:38:10.063Z</v>
+      </c>
+      <c r="R438" t="str">
+        <v>Payment Failed 🔴</v>
+      </c>
+      <c r="S438" t="str">
+        <v>payment_failed</v>
+      </c>
+      <c r="T438" t="str">
+        <v>6a2d957886f4fda65896f002</v>
+      </c>
+      <c r="U438" t="str">
+        <v>/account/orders/6a2d957886f4fda65896f002</v>
+      </c>
+    </row>
+    <row r="439" xml:space="preserve">
+      <c r="A439" t="str">
+        <v>6a2d958686f4fda65896f00a</v>
+      </c>
+      <c r="B439" t="str">
+        <v>6a2d957886f4fda65896f002</v>
+      </c>
+      <c r="C439" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="D439" t="str">
+        <v>admin</v>
+      </c>
+      <c r="E439" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="F439" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="G439" t="str" xml:space="preserve">
+        <v xml:space="preserve">Order #TCM-2026-0145 payment failed.
+Reason: User closed payment window
+Customer: Kavin M M
+Phone: 9600732162
+Email: mmkavin96@gmail.com
+Amount: ₹749</v>
+      </c>
+      <c r="H439" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="I439" t="str">
+        <v>true</v>
+      </c>
+      <c r="J439" t="str">
+        <v>false</v>
+      </c>
+      <c r="K439" t="str">
+        <v>false</v>
+      </c>
+      <c r="L439" t="str">
+        <v>false</v>
+      </c>
+      <c r="M439" t="str">
+        <v>2026-06-13T17:38:14.276Z</v>
+      </c>
+      <c r="N439" t="str">
+        <v>2026-06-13T17:38:14.277Z</v>
+      </c>
+      <c r="O439" t="str">
+        <v>2026-06-13T17:38:14.277Z</v>
+      </c>
+      <c r="P439" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q439" t="str">
+        <v>2026-06-13T17:38:14.648Z</v>
+      </c>
+      <c r="R439" t="str">
+        <v>⚠️ Payment Failed</v>
+      </c>
+      <c r="S439" t="str">
+        <v>admin_payment_failed</v>
+      </c>
+      <c r="T439" t="str">
+        <v>6a2d957886f4fda65896f002</v>
+      </c>
+      <c r="U439" t="str">
+        <v>/admin/orders</v>
+      </c>
+      <c r="V439" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="W439" t="str">
+        <v>9600732162</v>
+      </c>
+      <c r="X439" t="str">
+        <v>749</v>
+      </c>
+      <c r="AB439" t="str">
+        <v>mmkavin96@gmail.com</v>
+      </c>
+      <c r="AC439" t="str">
+        <v>User closed payment window</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD433"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD439"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/backend/exports/master_export.xlsx
+++ b/backend/exports/master_export.xlsx
@@ -413,27 +413,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S14"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="7.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="52.83203125" customWidth="1"/>
-    <col min="13" max="13" width="52.83203125" customWidth="1"/>
-    <col min="14" max="14" width="23.83203125" customWidth="1"/>
-    <col min="15" max="15" width="52.83203125" customWidth="1"/>
-    <col min="16" max="16" width="52.83203125" customWidth="1"/>
-    <col min="17" max="17" width="21.83203125" customWidth="1"/>
-    <col min="18" max="18" width="20.83203125" customWidth="1"/>
-    <col min="19" max="19" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -33621,7 +33600,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD465"/>
+  <dimension ref="A1:AD466"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" customWidth="1"/>
+    <col min="7" max="7" width="52.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="19.83203125" customWidth="1"/>
+    <col min="13" max="13" width="26.83203125" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="15" max="15" width="26.83203125" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" customWidth="1"/>
+    <col min="17" max="17" width="26.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -64057,9 +64055,74 @@
         <v>/admin/orders</v>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>6a3c123ca6a4b095dc8759d5</v>
+      </c>
+      <c r="B466" t="str">
+        <v>6a3c0b4b802ecd3f2584c5c3</v>
+      </c>
+      <c r="C466" t="str">
+        <v>69e9c1ab766ae41a5f9612cd</v>
+      </c>
+      <c r="D466" t="str">
+        <v>user</v>
+      </c>
+      <c r="E466" t="str">
+        <v>delivered</v>
+      </c>
+      <c r="F466" t="str">
+        <v>WEB</v>
+      </c>
+      <c r="G466" t="str">
+        <v>Your order #TCM-2026-0148 has been delivered.</v>
+      </c>
+      <c r="H466" t="str">
+        <v>SENT</v>
+      </c>
+      <c r="I466" t="str">
+        <v>true</v>
+      </c>
+      <c r="J466" t="str">
+        <v>false</v>
+      </c>
+      <c r="K466" t="str">
+        <v>false</v>
+      </c>
+      <c r="L466" t="str">
+        <v>false</v>
+      </c>
+      <c r="M466" t="str">
+        <v>2026-06-24T17:22:04.965Z</v>
+      </c>
+      <c r="N466" t="str">
+        <v>2026-06-24T17:22:04.966Z</v>
+      </c>
+      <c r="O466" t="str">
+        <v>2026-06-24T17:22:04.966Z</v>
+      </c>
+      <c r="P466" t="str">
+        <v>false</v>
+      </c>
+      <c r="Q466" t="str">
+        <v>2026-06-24T17:22:05.203Z</v>
+      </c>
+      <c r="R466" t="str">
+        <v>✅ Delivered</v>
+      </c>
+      <c r="S466" t="str">
+        <v>delivered</v>
+      </c>
+      <c r="T466" t="str">
+        <v>6a3c0b4b802ecd3f2584c5c3</v>
+      </c>
+      <c r="U466" t="str">
+        <v>/account/orders/6a3c0b4b802ecd3f2584c5c3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD465"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD466"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/backend/exports/master_export.xlsx
+++ b/backend/exports/master_export.xlsx
@@ -413,27 +413,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S14"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="7.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="52.83203125" customWidth="1"/>
-    <col min="13" max="13" width="52.83203125" customWidth="1"/>
-    <col min="14" max="14" width="23.83203125" customWidth="1"/>
-    <col min="15" max="15" width="52.83203125" customWidth="1"/>
-    <col min="16" max="16" width="11.83203125" customWidth="1"/>
-    <col min="17" max="17" width="21.83203125" customWidth="1"/>
-    <col min="18" max="18" width="20.83203125" customWidth="1"/>
-    <col min="19" max="19" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1166,15 +1145,6 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1334,49 +1304,6 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT155"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="13.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="21.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" customWidth="1"/>
-    <col min="11" max="11" width="52.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="14" width="16.83203125" customWidth="1"/>
-    <col min="15" max="15" width="19.83203125" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
-    <col min="17" max="17" width="20.83203125" customWidth="1"/>
-    <col min="18" max="18" width="15.83203125" customWidth="1"/>
-    <col min="19" max="19" width="15.83203125" customWidth="1"/>
-    <col min="20" max="20" width="18.83203125" customWidth="1"/>
-    <col min="21" max="21" width="15.83203125" customWidth="1"/>
-    <col min="22" max="22" width="18.83203125" customWidth="1"/>
-    <col min="23" max="23" width="15.83203125" customWidth="1"/>
-    <col min="24" max="24" width="17.83203125" customWidth="1"/>
-    <col min="25" max="25" width="52.83203125" customWidth="1"/>
-    <col min="26" max="26" width="14.83203125" customWidth="1"/>
-    <col min="27" max="27" width="17.83203125" customWidth="1"/>
-    <col min="28" max="28" width="20.83203125" customWidth="1"/>
-    <col min="29" max="29" width="19.83203125" customWidth="1"/>
-    <col min="30" max="30" width="22.83203125" customWidth="1"/>
-    <col min="31" max="31" width="26.83203125" customWidth="1"/>
-    <col min="32" max="32" width="26.83203125" customWidth="1"/>
-    <col min="33" max="33" width="26.83203125" customWidth="1"/>
-    <col min="34" max="34" width="20.83203125" customWidth="1"/>
-    <col min="35" max="35" width="52.83203125" customWidth="1"/>
-    <col min="36" max="36" width="15.83203125" customWidth="1"/>
-    <col min="37" max="37" width="26.83203125" customWidth="1"/>
-    <col min="38" max="38" width="13.83203125" customWidth="1"/>
-    <col min="39" max="39" width="26.83203125" customWidth="1"/>
-    <col min="40" max="40" width="19.83203125" customWidth="1"/>
-    <col min="41" max="41" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -18875,21 +18802,6 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M176"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="52.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="52.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -26117,20 +26029,6 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L10"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="40.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-    <col min="12" max="12" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -26522,28 +26420,6 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:T94"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="46.83203125" customWidth="1"/>
-    <col min="4" max="4" width="52.83203125" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="52.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="19.83203125" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
-    <col min="14" max="14" width="6.83203125" customWidth="1"/>
-    <col min="15" max="15" width="52.83203125" customWidth="1"/>
-    <col min="16" max="16" width="26.83203125" customWidth="1"/>
-    <col min="17" max="17" width="26.83203125" customWidth="1"/>
-    <col min="18" max="18" width="52.83203125" customWidth="1"/>
-    <col min="19" max="19" width="26.83203125" customWidth="1"/>
-    <col min="20" max="20" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -32418,7 +32294,7 @@
         <v>ewhWGq48FaDqw-lfBqoTAC:APA91bEEVn2ODZbo1gAzAqE5dK4Z4x-gwGuLzxaoEgvlQYbjNWgXIBxIczWIb0heL7QZOznQsJGlSVc8m6ZG-lsCncOjs6p3pGJiMv7I7eFm76-mcSBqFVs</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-06-27T10:35:35.500Z</v>
+        <v>2026-06-27T11:31:36.644Z</v>
       </c>
       <c r="D2" t="str">
         <v>iOS Device</v>
@@ -32427,7 +32303,7 @@
         <v>69e9c1ab766ae41a5f9612cd</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-06-27T10:36:35.222Z</v>
+        <v>2026-06-27T11:31:37.263Z</v>
       </c>
     </row>
   </sheetData>
@@ -32450,19 +32326,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AH51"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="7.83203125" customWidth="1"/>
-    <col min="7" max="7" width="42.83203125" customWidth="1"/>
-    <col min="8" max="8" width="42.83203125" customWidth="1"/>
-    <col min="9" max="9" width="52.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -34553,25 +34416,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AD493"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" customWidth="1"/>
-    <col min="6" max="6" width="9.83203125" customWidth="1"/>
-    <col min="7" max="7" width="52.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-    <col min="9" max="9" width="11.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="19.83203125" customWidth="1"/>
-    <col min="13" max="13" width="26.83203125" customWidth="1"/>
-    <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="15" max="15" width="26.83203125" customWidth="1"/>
-    <col min="16" max="16" width="8.83203125" customWidth="1"/>
-    <col min="17" max="17" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -66978,19 +66822,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K8"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="52.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-    <col min="9" max="9" width="52.83203125" customWidth="1"/>
-    <col min="10" max="10" width="33.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -67237,17 +67068,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="52.83203125" customWidth="1"/>
-    <col min="5" max="5" width="32.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -67404,19 +67224,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K4"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="52.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="49.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -67568,17 +67375,6 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I38"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="52.83203125" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="26.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -68692,24 +68488,6 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P4"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="29.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="19.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="19.83203125" customWidth="1"/>
-    <col min="12" max="12" width="52.83203125" customWidth="1"/>
-    <col min="13" max="13" width="52.83203125" customWidth="1"/>
-    <col min="14" max="14" width="26.83203125" customWidth="1"/>
-    <col min="15" max="15" width="26.83203125" customWidth="1"/>
-    <col min="16" max="16" width="26.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
